--- a/src/rodos_corpus/data/corpus/rendered/finance/REESTR-PLAT-20260908.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/REESTR-PLAT-20260908.xlsx
@@ -627,17 +627,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>УМС-2025/03</t>
+          <t>ЛД-2024/27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>АО «Уралметснаб»</t>
+          <t>ООО «Литейный двор»</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006612345678</t>
+          <t>005209876543</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -657,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЛД-2024/27</t>
+          <t>ИС-2025/21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ООО «Литейный двор»</t>
+          <t>ООО «Инструмент-Сервис»</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005209876543</t>
+          <t>005260011223</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ГЮ-2025/04</t>
+          <t>АТД-2025/06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>АО «Гидромаш-Юг»</t>
+          <t>ООО «Агротех-Деталь»</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006165223344</t>
+          <t>005401667788</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -717,17 +717,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ИС-2025/21</t>
+          <t>РСУ-2024/33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ООО «Инструмент-Сервис»</t>
+          <t>ООО «Ремсервис-Урал»</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005260011223</t>
+          <t>006671889900</t>
         </is>
       </c>
       <c r="D12" t="n">
